--- a/sheets/대금율보/검수/갈까부다.xlsx
+++ b/sheets/대금율보/검수/갈까부다.xlsx
@@ -5371,8 +5371,7 @@
         <is>
           <t xml:space="preserve">潢
 林
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="K4" s="23" t="inlineStr">
@@ -5383,8 +5382,7 @@
       <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">浹·
-汰∧
-‹</t>
+汰∧</t>
         </is>
       </c>
       <c r="M4" s="23" t="inlineStr">
@@ -5517,8 +5515,7 @@
         <is>
           <t xml:space="preserve">浹浹
 浹
-汰∧
-‹</t>
+汰∧</t>
         </is>
       </c>
       <c r="G6" s="26" t="inlineStr">
@@ -5542,8 +5539,7 @@
         <is>
           <t xml:space="preserve">潢汰∧
 潢
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="K6" s="26" t="inlineStr">
@@ -5555,8 +5551,7 @@
         <is>
           <t xml:space="preserve">浹浹
 浹汰∧
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="M6" s="26" t="inlineStr">
@@ -5568,8 +5563,7 @@
         <is>
           <t xml:space="preserve">–)
 –浹·
-汰∧
-‹</t>
+汰∧</t>
         </is>
       </c>
       <c r="O6" s="26" t="inlineStr">
@@ -5620,8 +5614,7 @@
         <is>
           <t xml:space="preserve">潢潢
 –
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
@@ -5672,8 +5665,7 @@
         <is>
           <t xml:space="preserve">浹浹
 浹汰
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -5697,8 +5689,7 @@
         <is>
           <t xml:space="preserve">汰∧
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
@@ -5734,8 +5725,7 @@
         <is>
           <t xml:space="preserve">浹浹
 –
-汰∧
-‹</t>
+汰∧</t>
         </is>
       </c>
       <c r="M8" s="23" t="inlineStr">
@@ -5772,7 +5762,7 @@
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹
+          <t xml:space="preserve">潢
 潢
 林</t>
         </is>
@@ -5908,8 +5898,7 @@
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="M10" s="26" t="inlineStr">
@@ -5948,8 +5937,7 @@
         <is>
           <t xml:space="preserve">潢
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -5972,7 +5960,7 @@
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋淋
-淋‹
+淋
 浹)</t>
         </is>
       </c>
@@ -6067,7 +6055,7 @@
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋汰∧
-林‹</t>
+林</t>
         </is>
       </c>
       <c r="K12" s="23" t="inlineStr">
@@ -6087,7 +6075,7 @@
       </c>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 㳞∧
 –</t>
         </is>
@@ -6128,8 +6116,7 @@
         <is>
           <t xml:space="preserve">∧汰淋
 淋淋
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
@@ -6178,8 +6165,7 @@
         <is>
           <t xml:space="preserve">淋
 汰∧
-淋
-‹</t>
+淋</t>
         </is>
       </c>
       <c r="C14" s="26" t="inlineStr">
@@ -6215,7 +6201,7 @@
         <is>
           <t xml:space="preserve">潕潕
 –潕
-淋‹</t>
+淋</t>
         </is>
       </c>
       <c r="I14" s="26" t="inlineStr">
@@ -6227,8 +6213,7 @@
         <is>
           <t xml:space="preserve">汰ㅅ
 淋
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="K14" s="26" t="inlineStr">
@@ -6398,8 +6383,7 @@
         <is>
           <t xml:space="preserve">林
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr">
@@ -6410,8 +6394,7 @@
       <c r="L16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="M16" s="23" t="inlineStr">
@@ -6423,8 +6406,7 @@
         <is>
           <t xml:space="preserve">–浹
 潢潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="O16" s="23" t="inlineStr">
@@ -6538,8 +6520,7 @@
         <is>
           <t xml:space="preserve">浹浹
 浹
-汰∧
-‹</t>
+汰∧</t>
         </is>
       </c>
       <c r="E18" s="26" t="inlineStr">

--- a/sheets/대금율보/검수/갈까부다.xlsx
+++ b/sheets/대금율보/검수/갈까부다.xlsx
@@ -5195,26 +5195,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="18.03" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="18.03" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="18.03" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="18.03" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="18.03" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="18.03" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="18.03" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="90.91" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="101.66" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="101.66" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="O4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="101.66" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="101.66" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="101.66" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="101.66" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="101.66" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="101.66" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="101.66" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="101.66" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="101.66" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
       <c r="N13" s="21"/>
       <c r="O13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="101.66" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="101.66" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="101.66" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="101.66" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="101.66" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -6595,6 +6595,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="44"/>
 </worksheet>
 </file>